--- a/DunbarLayout.xlsx
+++ b/DunbarLayout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevenbarlow/Documents/Athletics/Markings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49858A6B-39DC-2149-B8FE-28F4586D4867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31357B71-DC26-D843-8FEC-74DF00F901B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17380" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
   </bookViews>
@@ -5304,7 +5304,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FA7FA532-21A9-8D45-9DDB-79379004A0A8}" type="CELLRANGE">
+                    <a:fld id="{566CA2F4-D126-3A43-939B-3D154E19E24F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5336,7 +5336,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{85ED5F30-739C-234B-A453-7ADCC86B3A78}" type="CELLRANGE">
+                    <a:fld id="{7BF89025-D090-544C-A51E-74CCAC71F735}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5369,7 +5369,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD7E793D-DFA5-2C4B-A366-F893B1B4CD99}" type="CELLRANGE">
+                    <a:fld id="{7D18C9F7-2A84-8F48-A8EF-0A2D3276805A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5402,7 +5402,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{545BC2DC-532C-FD4B-B928-5D619581C0DB}" type="CELLRANGE">
+                    <a:fld id="{BE74AF3D-5CDE-7644-8B12-0D6BC9F40B0A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5435,7 +5435,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B4F69E2-8EC6-7A42-883E-4121F53FF30E}" type="CELLRANGE">
+                    <a:fld id="{746FBFDE-BBDF-9F47-85DD-E44E59D95E67}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5468,7 +5468,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25E4081A-FE73-2942-A4DB-8F66C26BF78E}" type="CELLRANGE">
+                    <a:fld id="{08D071CB-DA31-0B49-8974-3E50F9BD9B93}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5501,7 +5501,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{12714495-F3EF-2442-ADF8-C45BC2C2EF0D}" type="CELLRANGE">
+                    <a:fld id="{D2DFA8E1-FB7D-6E49-8D8E-20F1ACB0C82C}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5534,7 +5534,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D7F628A2-E55E-094F-BB8F-81E355DEDFCB}" type="CELLRANGE">
+                    <a:fld id="{9F372FC9-4C8B-B744-811E-8A3426F6B965}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5567,7 +5567,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{62E8EE1D-9ACD-7F4E-826C-211CF9F66056}" type="CELLRANGE">
+                    <a:fld id="{195A04B4-591F-504D-8D74-757E083DF300}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5600,7 +5600,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B33F9AE0-DFA7-AE4E-A733-461D232D7F3F}" type="CELLRANGE">
+                    <a:fld id="{88436A4F-6729-4848-B57D-72682FBF3515}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5633,7 +5633,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E7DBA5FF-0943-084E-B25E-F45343DD4C9B}" type="CELLRANGE">
+                    <a:fld id="{1C4E733B-3F64-5345-90D8-DFDF96E56A10}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5666,7 +5666,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{77EA517B-ED4D-F548-8930-D73C24EBCB23}" type="CELLRANGE">
+                    <a:fld id="{45AA12B4-2E2F-B84E-B099-CFB56A4D6C29}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5699,7 +5699,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D655B29-6444-D742-8BCF-A0A1039641AF}" type="CELLRANGE">
+                    <a:fld id="{52625B52-504D-644D-91A8-FD7EEAD28C2C}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5732,7 +5732,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B908B82B-D0D2-B947-BCB5-84117DA130AB}" type="CELLRANGE">
+                    <a:fld id="{D9DC1309-F2F0-6540-8C23-2F65A398A0DC}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5765,7 +5765,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E4E6A1B1-3B91-374F-B865-325F0B1074E9}" type="CELLRANGE">
+                    <a:fld id="{1BF2EF62-B9BB-B141-93E3-5E9F13B6C1ED}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5798,7 +5798,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CCDC2B8F-D1EE-8342-BBD7-01A6F2FB8096}" type="CELLRANGE">
+                    <a:fld id="{4EE19249-DE06-7341-84AB-730C2BFDA316}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5831,7 +5831,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{080679E5-3248-4149-BBE4-B65B5EF7CC54}" type="CELLRANGE">
+                    <a:fld id="{BAE5284B-40AF-6545-B37E-14BB5D271AFF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5864,7 +5864,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{63E25A64-2B5D-1C48-80A2-8E71366101BD}" type="CELLRANGE">
+                    <a:fld id="{9A8027CD-3323-DC45-9F6E-8F6EC4D0296F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5897,7 +5897,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A43B471C-0635-9347-AB6F-889F4F917E4C}" type="CELLRANGE">
+                    <a:fld id="{AD52E931-45F5-1946-B265-F9CE8E4D5760}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5930,7 +5930,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{10521C8E-504C-CD4E-9067-415D23431D3D}" type="CELLRANGE">
+                    <a:fld id="{07F7E47E-DCCC-6D4C-9B8B-85F77C1F16FD}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5963,7 +5963,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E742C6D5-4ACC-5C46-BAB0-0966995C3433}" type="CELLRANGE">
+                    <a:fld id="{4116DD56-881A-3944-BB1D-AFE230A471F4}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9134,7 +9134,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8BFC01FB-4652-EA4E-BBA2-1DBB973B9CCB}" type="CELLRANGE">
+                    <a:fld id="{6C5407C7-3108-FB4B-9342-633E885C3D37}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>

--- a/DunbarLayout.xlsx
+++ b/DunbarLayout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevenbarlow/Documents/Athletics/Markings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31357B71-DC26-D843-8FEC-74DF00F901B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA99DBC-C1B2-C746-A78D-AF74D5CC6C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17380" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
   </bookViews>
@@ -5304,7 +5304,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{566CA2F4-D126-3A43-939B-3D154E19E24F}" type="CELLRANGE">
+                    <a:fld id="{A868880E-8208-0543-8FC3-12A6987F4D8C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5336,7 +5336,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7BF89025-D090-544C-A51E-74CCAC71F735}" type="CELLRANGE">
+                    <a:fld id="{38DDAB1B-3369-2C4F-9F8C-78FF151322D1}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5369,7 +5369,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7D18C9F7-2A84-8F48-A8EF-0A2D3276805A}" type="CELLRANGE">
+                    <a:fld id="{7A85A29F-2AFA-4244-A8A9-E357182AF61D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5402,7 +5402,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BE74AF3D-5CDE-7644-8B12-0D6BC9F40B0A}" type="CELLRANGE">
+                    <a:fld id="{F5E0A083-2801-CD4D-B9C6-43C24288B82D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5435,7 +5435,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{746FBFDE-BBDF-9F47-85DD-E44E59D95E67}" type="CELLRANGE">
+                    <a:fld id="{EB077C23-02B0-8E47-8F97-DD61B230A7A6}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5468,7 +5468,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{08D071CB-DA31-0B49-8974-3E50F9BD9B93}" type="CELLRANGE">
+                    <a:fld id="{638E16FF-DCF9-9742-B966-85FF90936F68}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5501,7 +5501,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D2DFA8E1-FB7D-6E49-8D8E-20F1ACB0C82C}" type="CELLRANGE">
+                    <a:fld id="{6CD9F27B-BBBE-0D4C-9656-057ABEC7B26D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5534,7 +5534,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9F372FC9-4C8B-B744-811E-8A3426F6B965}" type="CELLRANGE">
+                    <a:fld id="{3A4C4B3A-183A-6B4F-8139-3A585B848F0F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5567,7 +5567,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{195A04B4-591F-504D-8D74-757E083DF300}" type="CELLRANGE">
+                    <a:fld id="{070C4772-88FC-994F-B1D4-2AA0B33FA836}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5600,7 +5600,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{88436A4F-6729-4848-B57D-72682FBF3515}" type="CELLRANGE">
+                    <a:fld id="{0ADF6AF9-C806-7F40-81BB-D0253400C085}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5633,7 +5633,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1C4E733B-3F64-5345-90D8-DFDF96E56A10}" type="CELLRANGE">
+                    <a:fld id="{FD57E198-42D3-154C-B328-7104403C7943}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5666,7 +5666,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{45AA12B4-2E2F-B84E-B099-CFB56A4D6C29}" type="CELLRANGE">
+                    <a:fld id="{1DCB7032-B1CE-BF40-A225-03FF50ADA1F9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5699,7 +5699,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{52625B52-504D-644D-91A8-FD7EEAD28C2C}" type="CELLRANGE">
+                    <a:fld id="{564062BF-A926-0C44-AE6B-507BE12B65EF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5732,7 +5732,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D9DC1309-F2F0-6540-8C23-2F65A398A0DC}" type="CELLRANGE">
+                    <a:fld id="{919D03D3-3473-414C-9D76-4FA19F650333}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5765,7 +5765,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1BF2EF62-B9BB-B141-93E3-5E9F13B6C1ED}" type="CELLRANGE">
+                    <a:fld id="{DE08BCEB-F3CD-D741-985A-1CDAD1D18F93}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5798,7 +5798,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4EE19249-DE06-7341-84AB-730C2BFDA316}" type="CELLRANGE">
+                    <a:fld id="{0F07E109-89F1-354E-BA58-1758502BD30B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5831,7 +5831,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BAE5284B-40AF-6545-B37E-14BB5D271AFF}" type="CELLRANGE">
+                    <a:fld id="{48AAC21C-5C18-6243-8B93-7B3C3A3B1E7A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5864,7 +5864,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9A8027CD-3323-DC45-9F6E-8F6EC4D0296F}" type="CELLRANGE">
+                    <a:fld id="{84830C99-3EC1-014D-93CA-4E1FE57FC60A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5897,7 +5897,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AD52E931-45F5-1946-B265-F9CE8E4D5760}" type="CELLRANGE">
+                    <a:fld id="{990ED1D2-9B75-A44F-A4F9-0AAFDEBCE56B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5930,7 +5930,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{07F7E47E-DCCC-6D4C-9B8B-85F77C1F16FD}" type="CELLRANGE">
+                    <a:fld id="{86C29A59-F955-CA44-B1DC-2709254D014D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5963,7 +5963,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4116DD56-881A-3944-BB1D-AFE230A471F4}" type="CELLRANGE">
+                    <a:fld id="{0836884E-DF84-244F-8D04-42E8DF9256E7}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9134,7 +9134,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6C5407C7-3108-FB4B-9342-633E885C3D37}" type="CELLRANGE">
+                    <a:fld id="{0893B05A-4ACA-454B-BB40-B5260470C859}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9244,7 +9244,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>76.89</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>120.35708960898624</c:v>
@@ -9259,7 +9259,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>-38.99</c:v>
+                  <c:v>38.99</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>11.98833687065725</c:v>
@@ -9275,7 +9275,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>130.71</c:v>
+                    <c:v>51.17</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -10398,15 +10398,15 @@
         <v>74</v>
       </c>
       <c r="T3" s="40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U3" s="42">
         <f>IFERROR(VLOOKUP(T3,AllPoints,2,FALSE),0)</f>
-        <v>0</v>
+        <v>76.89</v>
       </c>
       <c r="V3" s="43">
         <f>IFERROR(VLOOKUP(T3,AllPoints,3,FALSE),0)</f>
-        <v>-38.99</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="4" spans="19:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -10431,15 +10431,15 @@
       </c>
       <c r="T5" s="41">
         <f>SQRT((U4-U3)^2+(V4-V3)^2)</f>
-        <v>130.70814760084298</v>
+        <v>51.171063022240872</v>
       </c>
       <c r="U5" s="44">
         <f>ABS(U4-U3)</f>
-        <v>120.35708960898624</v>
+        <v>43.467089608986242</v>
       </c>
       <c r="V5" s="45">
         <f>ABS(V4-V3)</f>
-        <v>50.978336870657252</v>
+        <v>27.001663129342752</v>
       </c>
     </row>
     <row r="15" spans="19:22" x14ac:dyDescent="0.2">
@@ -39951,7 +39951,7 @@
         <v>2</v>
       </c>
       <c r="L5">
-        <f>L4-35</f>
+        <f t="shared" ref="L5:L13" si="6">L4-35</f>
         <v>320</v>
       </c>
     </row>
@@ -39987,7 +39987,7 @@
         <v>3</v>
       </c>
       <c r="L6">
-        <f>L5-35</f>
+        <f t="shared" si="6"/>
         <v>285</v>
       </c>
     </row>
@@ -40023,7 +40023,7 @@
         <v>4</v>
       </c>
       <c r="L7">
-        <f>L6-35</f>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
     </row>
@@ -40059,7 +40059,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <f>L7-35</f>
+        <f t="shared" si="6"/>
         <v>215</v>
       </c>
     </row>
@@ -40095,7 +40095,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <f>L8-35</f>
+        <f t="shared" si="6"/>
         <v>180</v>
       </c>
     </row>
@@ -40131,7 +40131,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <f>L9-35</f>
+        <f t="shared" si="6"/>
         <v>145</v>
       </c>
     </row>
@@ -40155,18 +40155,18 @@
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" ref="F11:F26" si="6">(Straight-(IF(D11&gt;VLOOKUP(E11,Data,4,FALSE),1,D11/VLOOKUP(E11,Data,4,FALSE)))*Straight+(IF(D11&gt;VLOOKUP(E11,Data,9,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,8,FALSE),(D11-VLOOKUP(E11,Data,8,FALSE))/VLOOKUP(E11,Data,6,FALSE),0)))*Straight)-VLOOKUP(E11,Data,2,FALSE)*SIN(RADIANS(180*(IF(D11&gt;VLOOKUP(E11,Data,8,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,4,FALSE),(D11-VLOOKUP(E11,Data,4,FALSE))/VLOOKUP(E11,Data,5,FALSE),0)))+180*(IF(D11&gt;VLOOKUP(E11,Data,10,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,9,FALSE),(D11-VLOOKUP(E11,Data,9,FALSE))/VLOOKUP(E11,Data,7,FALSE),0)))))</f>
+        <f t="shared" ref="F11:F26" si="7">(Straight-(IF(D11&gt;VLOOKUP(E11,Data,4,FALSE),1,D11/VLOOKUP(E11,Data,4,FALSE)))*Straight+(IF(D11&gt;VLOOKUP(E11,Data,9,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,8,FALSE),(D11-VLOOKUP(E11,Data,8,FALSE))/VLOOKUP(E11,Data,6,FALSE),0)))*Straight)-VLOOKUP(E11,Data,2,FALSE)*SIN(RADIANS(180*(IF(D11&gt;VLOOKUP(E11,Data,8,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,4,FALSE),(D11-VLOOKUP(E11,Data,4,FALSE))/VLOOKUP(E11,Data,5,FALSE),0)))+180*(IF(D11&gt;VLOOKUP(E11,Data,10,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,9,FALSE),(D11-VLOOKUP(E11,Data,9,FALSE))/VLOOKUP(E11,Data,7,FALSE),0)))))</f>
         <v>111.64106706192882</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" ref="G11:G26" si="7">-VLOOKUP(E11,Data,2,FALSE)*COS(RADIANS(180*(IF(D11&gt;VLOOKUP(E11,Data,8,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,4,FALSE),(D11-VLOOKUP(E11,Data,4,FALSE))/VLOOKUP(E11,Data,5,FALSE),0)))+180*(IF(D11&gt;VLOOKUP(E11,Data,10,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,9,FALSE),(D11-VLOOKUP(E11,Data,9,FALSE))/VLOOKUP(E11,Data,7,FALSE),0)))))</f>
+        <f t="shared" ref="G11:G26" si="8">-VLOOKUP(E11,Data,2,FALSE)*COS(RADIANS(180*(IF(D11&gt;VLOOKUP(E11,Data,8,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,4,FALSE),(D11-VLOOKUP(E11,Data,4,FALSE))/VLOOKUP(E11,Data,5,FALSE),0)))+180*(IF(D11&gt;VLOOKUP(E11,Data,10,FALSE),1,IF(D11&gt;VLOOKUP(E11,Data,9,FALSE),(D11-VLOOKUP(E11,Data,9,FALSE))/VLOOKUP(E11,Data,7,FALSE),0)))))</f>
         <v>17.680029356800436</v>
       </c>
       <c r="K11">
         <v>8</v>
       </c>
       <c r="L11">
-        <f>L10-35</f>
+        <f t="shared" si="6"/>
         <v>110</v>
       </c>
     </row>
@@ -40191,18 +40191,18 @@
         <v>2</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>110.10637504775183</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>22.660903086309023</v>
       </c>
       <c r="K12">
         <v>9</v>
       </c>
       <c r="L12">
-        <f>L11-35</f>
+        <f t="shared" si="6"/>
         <v>75</v>
       </c>
     </row>
@@ -40212,11 +40212,11 @@
         <v>H-2-3</v>
       </c>
       <c r="B13">
-        <f t="shared" ref="B13:C18" si="8">B12</f>
+        <f t="shared" ref="B13:C18" si="9">B12</f>
         <v>320</v>
       </c>
       <c r="C13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D13" s="1">
@@ -40227,18 +40227,18 @@
         <v>3</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>108.05782410739477</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>27.294901362901133</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13">
-        <f>L12-35</f>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -40248,11 +40248,11 @@
         <v>H-2-4</v>
       </c>
       <c r="B14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>320</v>
       </c>
       <c r="C14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D14" s="1">
@@ -40263,11 +40263,11 @@
         <v>4</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>105.58082415722299</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>31.557235448931664</v>
       </c>
     </row>
@@ -40277,11 +40277,11 @@
         <v>H-2-5</v>
       </c>
       <c r="B15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>320</v>
       </c>
       <c r="C15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D15" s="1">
@@ -40292,11 +40292,11 @@
         <v>5</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>102.75213646530401</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>35.43623565575205</v>
       </c>
     </row>
@@ -40306,11 +40306,11 @@
         <v>H-2-6</v>
       </c>
       <c r="B16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>320</v>
       </c>
       <c r="C16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D16" s="1">
@@ -40321,11 +40321,11 @@
         <v>6</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>99.639810746204745</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>38.93011958640593</v>
       </c>
     </row>
@@ -40335,11 +40335,11 @@
         <v>H-2-7</v>
       </c>
       <c r="B17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>320</v>
       </c>
       <c r="C17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D17" s="1">
@@ -40350,11 +40350,11 @@
         <v>7</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>96.303514230980596</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>42.044399926785893</v>
       </c>
     </row>
@@ -40364,11 +40364,11 @@
         <v>H-2-8</v>
       </c>
       <c r="B18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>320</v>
       </c>
       <c r="C18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D18" s="1">
@@ -40379,11 +40379,11 @@
         <v>8</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>92.795088300396159</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>44.789832173793648</v>
       </c>
     </row>
@@ -40407,11 +40407,11 @@
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>84.904877087117455</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>38.157330164444154</v>
       </c>
     </row>
@@ -40436,11 +40436,11 @@
         <v>2</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>81.141936464815245</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>39.984561224292243</v>
       </c>
     </row>
@@ -40450,11 +40450,11 @@
         <v>H-3-3</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:C26" si="9">B20</f>
+        <f t="shared" ref="B21:C26" si="10">B20</f>
         <v>285</v>
       </c>
       <c r="C21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="D21" s="1">
@@ -40465,11 +40465,11 @@
         <v>3</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>77.336183184677466</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>41.42759733035107</v>
       </c>
     </row>
@@ -40479,11 +40479,11 @@
         <v>H-3-4</v>
       </c>
       <c r="B22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
       <c r="C22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="D22" s="1">
@@ -40494,11 +40494,11 @@
         <v>4</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>73.505602727889539</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>42.65</v>
       </c>
     </row>
@@ -40508,11 +40508,11 @@
         <v>H-3-5</v>
       </c>
       <c r="B23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
       <c r="C23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="D23" s="1">
@@ -40523,11 +40523,11 @@
         <v>5</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>69.672859690509995</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>43.87</v>
       </c>
     </row>
@@ -40537,11 +40537,11 @@
         <v>H-3-6</v>
       </c>
       <c r="B24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
       <c r="C24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="D24" s="1">
@@ -40552,11 +40552,11 @@
         <v>6</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>65.840116653130451</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>45.089999999999996</v>
       </c>
     </row>
@@ -40566,11 +40566,11 @@
         <v>H-3-7</v>
       </c>
       <c r="B25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
       <c r="C25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="D25" s="1">
@@ -40581,11 +40581,11 @@
         <v>7</v>
       </c>
       <c r="F25" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>62.0073736157509</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>46.309999999999995</v>
       </c>
     </row>
@@ -40595,11 +40595,11 @@
         <v>H-3-8</v>
       </c>
       <c r="B26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
       <c r="C26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="D26" s="1">
@@ -40610,11 +40610,11 @@
         <v>8</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>58.174630578371357</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>47.529999999999994</v>
       </c>
     </row>
@@ -40648,7 +40648,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <f t="shared" ref="A28:A34" si="10">CONCATENATE("H-",C28,"-",E28)</f>
+        <f t="shared" ref="A28:A34" si="11">CONCATENATE("H-",C28,"-",E28)</f>
         <v>H-4-2</v>
       </c>
       <c r="B28">
@@ -40677,15 +40677,15 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>H-4-3</v>
       </c>
       <c r="B29">
-        <f t="shared" ref="B29:B34" si="11">B28</f>
+        <f t="shared" ref="B29:B34" si="12">B28</f>
         <v>250</v>
       </c>
       <c r="C29">
-        <f t="shared" ref="C29:C34" si="12">C28</f>
+        <f t="shared" ref="C29:C34" si="13">C28</f>
         <v>4</v>
       </c>
       <c r="D29" s="1">
@@ -40706,15 +40706,15 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>H-4-4</v>
       </c>
       <c r="B30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>250</v>
       </c>
       <c r="C30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="D30" s="1">
@@ -40735,15 +40735,15 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>H-4-5</v>
       </c>
       <c r="B31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>250</v>
       </c>
       <c r="C31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="D31" s="1">
@@ -40764,15 +40764,15 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>H-4-6</v>
       </c>
       <c r="B32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>250</v>
       </c>
       <c r="C32">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="D32" s="1">
@@ -40793,15 +40793,15 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>H-4-7</v>
       </c>
       <c r="B33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>250</v>
       </c>
       <c r="C33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="D33" s="1">
@@ -40822,15 +40822,15 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>H-4-8</v>
       </c>
       <c r="B34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>250</v>
       </c>
       <c r="C34">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="D34" s="1">
@@ -40879,7 +40879,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <f t="shared" ref="A36:A42" si="13">CONCATENATE("H-",C36,"-",E36)</f>
+        <f t="shared" ref="A36:A42" si="14">CONCATENATE("H-",C36,"-",E36)</f>
         <v>H-5-2</v>
       </c>
       <c r="B36">
@@ -40908,15 +40908,15 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H-5-3</v>
       </c>
       <c r="B37">
-        <f t="shared" ref="B37:B42" si="14">B36</f>
+        <f t="shared" ref="B37:B42" si="15">B36</f>
         <v>215</v>
       </c>
       <c r="C37">
-        <f t="shared" ref="C37:C42" si="15">C36</f>
+        <f t="shared" ref="C37:C42" si="16">C36</f>
         <v>5</v>
       </c>
       <c r="D37" s="1">
@@ -40937,15 +40937,15 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H-5-4</v>
       </c>
       <c r="B38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="C38">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="D38" s="1">
@@ -40966,15 +40966,15 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H-5-5</v>
       </c>
       <c r="B39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="C39">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="D39" s="1">
@@ -40995,15 +40995,15 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H-5-6</v>
       </c>
       <c r="B40">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="C40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="D40" s="1">
@@ -41024,15 +41024,15 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H-5-7</v>
       </c>
       <c r="B41">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="C41">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="D41" s="1">
@@ -41053,15 +41053,15 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H-5-8</v>
       </c>
       <c r="B42">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="C42">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="D42" s="1">
@@ -41110,7 +41110,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="str">
-        <f t="shared" ref="A44:A50" si="16">CONCATENATE("H-",C44,"-",E44)</f>
+        <f t="shared" ref="A44:A50" si="17">CONCATENATE("H-",C44,"-",E44)</f>
         <v>H-6-2</v>
       </c>
       <c r="B44">
@@ -41139,15 +41139,15 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>H-6-3</v>
       </c>
       <c r="B45">
-        <f t="shared" ref="B45:B50" si="17">B44</f>
+        <f t="shared" ref="B45:B50" si="18">B44</f>
         <v>180</v>
       </c>
       <c r="C45">
-        <f t="shared" ref="C45:C50" si="18">C44</f>
+        <f t="shared" ref="C45:C50" si="19">C44</f>
         <v>6</v>
       </c>
       <c r="D45" s="1">
@@ -41168,15 +41168,15 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>H-6-4</v>
       </c>
       <c r="B46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="C46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="D46" s="1">
@@ -41197,15 +41197,15 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>H-6-5</v>
       </c>
       <c r="B47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="C47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="D47" s="1">
@@ -41226,15 +41226,15 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>H-6-6</v>
       </c>
       <c r="B48">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="C48">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="D48" s="1">
@@ -41255,15 +41255,15 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>H-6-7</v>
       </c>
       <c r="B49">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="C49">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="D49" s="1">
@@ -41284,15 +41284,15 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>H-6-8</v>
       </c>
       <c r="B50">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="C50">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
       <c r="D50" s="1">
@@ -41324,24 +41324,24 @@
         <v>7</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" ref="D51:D82" si="19">B51*DIstanceMultiplier</f>
+        <f t="shared" ref="D51:D82" si="20">B51*DIstanceMultiplier</f>
         <v>145.00653666828339</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51" s="1">
-        <f t="shared" ref="F51:F82" si="20">(Straight-(IF(D51&gt;VLOOKUP(E51,Data,4,FALSE),1,D51/VLOOKUP(E51,Data,4,FALSE)))*Straight+(IF(D51&gt;VLOOKUP(E51,Data,9,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,8,FALSE),(D51-VLOOKUP(E51,Data,8,FALSE))/VLOOKUP(E51,Data,6,FALSE),0)))*Straight)-VLOOKUP(E51,Data,2,FALSE)*SIN(RADIANS(180*(IF(D51&gt;VLOOKUP(E51,Data,8,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,4,FALSE),(D51-VLOOKUP(E51,Data,4,FALSE))/VLOOKUP(E51,Data,5,FALSE),0)))+180*(IF(D51&gt;VLOOKUP(E51,Data,10,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,9,FALSE),(D51-VLOOKUP(E51,Data,9,FALSE))/VLOOKUP(E51,Data,7,FALSE),0)))))</f>
+        <f t="shared" ref="F51:F82" si="21">(Straight-(IF(D51&gt;VLOOKUP(E51,Data,4,FALSE),1,D51/VLOOKUP(E51,Data,4,FALSE)))*Straight+(IF(D51&gt;VLOOKUP(E51,Data,9,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,8,FALSE),(D51-VLOOKUP(E51,Data,8,FALSE))/VLOOKUP(E51,Data,6,FALSE),0)))*Straight)-VLOOKUP(E51,Data,2,FALSE)*SIN(RADIANS(180*(IF(D51&gt;VLOOKUP(E51,Data,8,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,4,FALSE),(D51-VLOOKUP(E51,Data,4,FALSE))/VLOOKUP(E51,Data,5,FALSE),0)))+180*(IF(D51&gt;VLOOKUP(E51,Data,10,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,9,FALSE),(D51-VLOOKUP(E51,Data,9,FALSE))/VLOOKUP(E51,Data,7,FALSE),0)))))</f>
         <v>-38.445530569292728</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" ref="G51:G82" si="21">-VLOOKUP(E51,Data,2,FALSE)*COS(RADIANS(180*(IF(D51&gt;VLOOKUP(E51,Data,8,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,4,FALSE),(D51-VLOOKUP(E51,Data,4,FALSE))/VLOOKUP(E51,Data,5,FALSE),0)))+180*(IF(D51&gt;VLOOKUP(E51,Data,10,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,9,FALSE),(D51-VLOOKUP(E51,Data,9,FALSE))/VLOOKUP(E51,Data,7,FALSE),0)))))</f>
+        <f t="shared" ref="G51:G82" si="22">-VLOOKUP(E51,Data,2,FALSE)*COS(RADIANS(180*(IF(D51&gt;VLOOKUP(E51,Data,8,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,4,FALSE),(D51-VLOOKUP(E51,Data,4,FALSE))/VLOOKUP(E51,Data,5,FALSE),0)))+180*(IF(D51&gt;VLOOKUP(E51,Data,10,FALSE),1,IF(D51&gt;VLOOKUP(E51,Data,9,FALSE),(D51-VLOOKUP(E51,Data,9,FALSE))/VLOOKUP(E51,Data,7,FALSE),0)))))</f>
         <v>6.4931717400341897</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="str">
-        <f t="shared" ref="A52:A58" si="22">CONCATENATE("H-",C52,"-",E52)</f>
+        <f t="shared" ref="A52:A58" si="23">CONCATENATE("H-",C52,"-",E52)</f>
         <v>H-7-2</v>
       </c>
       <c r="B52">
@@ -41353,192 +41353,192 @@
         <v>7</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>145.00653666828339</v>
       </c>
       <c r="E52">
         <v>2</v>
       </c>
       <c r="F52" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-39.945145112746069</v>
       </c>
       <c r="G52" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.6075461931117792</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>H-7-3</v>
       </c>
       <c r="B53">
-        <f t="shared" ref="B53:B58" si="23">B52</f>
+        <f t="shared" ref="B53:B58" si="24">B52</f>
         <v>145</v>
       </c>
       <c r="C53">
-        <f t="shared" ref="C53:C58" si="24">C52</f>
+        <f t="shared" ref="C53:C58" si="25">C52</f>
         <v>7</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>145.00653666828339</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-41.34132067316807</v>
       </c>
       <c r="G53" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.7092628145468716</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>H-7-4</v>
       </c>
       <c r="B54">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>145</v>
       </c>
       <c r="C54">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>145.00653666828339</v>
       </c>
       <c r="E54">
         <v>4</v>
       </c>
       <c r="F54" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-42.642419377687176</v>
       </c>
       <c r="G54" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.80409552756439973</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>H-7-5</v>
       </c>
       <c r="B55">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>145</v>
       </c>
       <c r="C55">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>145.00653666828339</v>
       </c>
       <c r="E55">
         <v>5</v>
       </c>
       <c r="F55" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-43.856123923102061</v>
       </c>
       <c r="G55" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-1.1033106731625659</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>H-7-6</v>
       </c>
       <c r="B56">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>145</v>
       </c>
       <c r="C56">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>145.00653666828339</v>
       </c>
       <c r="E56">
         <v>6</v>
       </c>
       <c r="F56" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-44.989472286508523</v>
       </c>
       <c r="G56" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-3.0092330221305645</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>H-7-7</v>
       </c>
       <c r="B57">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>145</v>
       </c>
       <c r="C57">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>145.00653666828339</v>
       </c>
       <c r="E57">
         <v>7</v>
       </c>
       <c r="F57" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-46.048898999844305</v>
       </c>
       <c r="G57" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-4.9107026892429104</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>H-7-8</v>
       </c>
       <c r="B58">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>145</v>
       </c>
       <c r="C58">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>145.00653666828339</v>
       </c>
       <c r="E58">
         <v>8</v>
       </c>
       <c r="F58" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-47.04027925063054</v>
       </c>
       <c r="G58" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-6.8053675890944527</v>
       </c>
     </row>
@@ -41555,24 +41555,24 @@
         <v>8</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-29.163003299198994</v>
       </c>
       <c r="G59" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-25.879322606492405</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="str">
-        <f t="shared" ref="A60:A66" si="25">CONCATENATE("H-",C60,"-",E60)</f>
+        <f t="shared" ref="A60:A66" si="26">CONCATENATE("H-",C60,"-",E60)</f>
         <v>H-8-2</v>
       </c>
       <c r="B60">
@@ -41584,192 +41584,192 @@
         <v>8</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E60">
         <v>2</v>
       </c>
       <c r="F60" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-29.38495031138708</v>
       </c>
       <c r="G60" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-27.447564467495329</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>H-8-3</v>
       </c>
       <c r="B61">
-        <f t="shared" ref="B61:B66" si="26">B60</f>
+        <f t="shared" ref="B61:B66" si="27">B60</f>
         <v>110</v>
       </c>
       <c r="C61">
-        <f t="shared" ref="C61:C66" si="27">C60</f>
+        <f t="shared" ref="C61:C66" si="28">C60</f>
         <v>8</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-29.588683385662058</v>
       </c>
       <c r="G61" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-28.999219222300557</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>H-8-4</v>
       </c>
       <c r="B62">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>110</v>
       </c>
       <c r="C62">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E62">
         <v>4</v>
       </c>
       <c r="F62" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-29.776125558281276</v>
       </c>
       <c r="G62" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-30.535304922948917</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>H-8-5</v>
       </c>
       <c r="B63">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>110</v>
       </c>
       <c r="C63">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E63">
         <v>5</v>
       </c>
       <c r="F63" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-29.948955401614509</v>
       </c>
       <c r="G63" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-32.056777292050192</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>H-8-6</v>
       </c>
       <c r="B64">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>110</v>
       </c>
       <c r="C64">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E64">
         <v>6</v>
       </c>
       <c r="F64" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-30.108642917705101</v>
       </c>
       <c r="G64" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-33.564530708087162</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>H-8-7</v>
       </c>
       <c r="B65">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>110</v>
       </c>
       <c r="C65">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E65">
         <v>7</v>
       </c>
       <c r="F65" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-30.256479519418686</v>
       </c>
       <c r="G65" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-35.059400267132311</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>H-8-8</v>
       </c>
       <c r="B66">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>110</v>
       </c>
       <c r="C66">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>110.00495885180121</v>
       </c>
       <c r="E66">
         <v>8</v>
       </c>
       <c r="F66" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-30.393603167924773</v>
       </c>
       <c r="G66" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-36.542164501719277</v>
       </c>
     </row>
@@ -41786,24 +41786,24 @@
         <v>9</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G67" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-38.99</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="str">
-        <f t="shared" ref="A68:A74" si="28">CONCATENATE("H-",C68,"-",E68)</f>
+        <f t="shared" ref="A68:A74" si="29">CONCATENATE("H-",C68,"-",E68)</f>
         <v>H-9-2</v>
       </c>
       <c r="B68">
@@ -41815,192 +41815,192 @@
         <v>9</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E68">
         <v>2</v>
       </c>
       <c r="F68" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G68" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-40.21</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>H-9-3</v>
       </c>
       <c r="B69">
-        <f t="shared" ref="B69:B74" si="29">B68</f>
+        <f t="shared" ref="B69:B74" si="30">B68</f>
         <v>75</v>
       </c>
       <c r="C69">
-        <f t="shared" ref="C69:C74" si="30">C68</f>
+        <f t="shared" ref="C69:C74" si="31">C68</f>
         <v>9</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E69">
         <v>3</v>
       </c>
       <c r="F69" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G69" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-41.43</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>H-9-4</v>
       </c>
       <c r="B70">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>75</v>
       </c>
       <c r="C70">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E70">
         <v>4</v>
       </c>
       <c r="F70" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G70" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-42.65</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>H-9-5</v>
       </c>
       <c r="B71">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>75</v>
       </c>
       <c r="C71">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E71">
         <v>5</v>
       </c>
       <c r="F71" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G71" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-43.87</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>H-9-6</v>
       </c>
       <c r="B72">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>75</v>
       </c>
       <c r="C72">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E72">
         <v>6</v>
       </c>
       <c r="F72" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-45.089999999999996</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>H-9-7</v>
       </c>
       <c r="B73">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>75</v>
       </c>
       <c r="C73">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E73">
         <v>7</v>
       </c>
       <c r="F73" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-46.309999999999995</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>H-9-8</v>
       </c>
       <c r="B74">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>75</v>
       </c>
       <c r="C74">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>75.003381035318995</v>
       </c>
       <c r="E74">
         <v>8</v>
       </c>
       <c r="F74" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8866189646810057</v>
       </c>
       <c r="G74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-47.529999999999994</v>
       </c>
     </row>
@@ -42017,24 +42017,24 @@
         <v>10</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-38.99</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="str">
-        <f t="shared" ref="A76:A82" si="31">CONCATENATE("H-",C76,"-",E76)</f>
+        <f t="shared" ref="A76:A82" si="32">CONCATENATE("H-",C76,"-",E76)</f>
         <v>H-10-2</v>
       </c>
       <c r="B76">
@@ -42046,192 +42046,192 @@
         <v>10</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E76">
         <v>2</v>
       </c>
       <c r="F76" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-40.21</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>H-10-3</v>
       </c>
       <c r="B77">
-        <f t="shared" ref="B77:B82" si="32">B76</f>
+        <f t="shared" ref="B77:B82" si="33">B76</f>
         <v>40</v>
       </c>
       <c r="C77">
-        <f t="shared" ref="C77:C82" si="33">C76</f>
+        <f t="shared" ref="C77:C82" si="34">C76</f>
         <v>10</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-41.43</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>H-10-4</v>
       </c>
       <c r="B78">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="C78">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E78">
         <v>4</v>
       </c>
       <c r="F78" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-42.65</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>H-10-5</v>
       </c>
       <c r="B79">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="C79">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E79">
         <v>5</v>
       </c>
       <c r="F79" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-43.87</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>H-10-6</v>
       </c>
       <c r="B80">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="C80">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E80">
         <v>6</v>
       </c>
       <c r="F80" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G80" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-45.089999999999996</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>H-10-7</v>
       </c>
       <c r="B81">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="C81">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E81">
         <v>7</v>
       </c>
       <c r="F81" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-46.309999999999995</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>H-10-8</v>
       </c>
       <c r="B82">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>40</v>
       </c>
       <c r="C82">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.001803218836798</v>
       </c>
       <c r="E82">
         <v>8</v>
       </c>
       <c r="F82" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36.888196781163202</v>
       </c>
       <c r="G82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-47.529999999999994</v>
       </c>
     </row>

--- a/DunbarLayout.xlsx
+++ b/DunbarLayout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevenbarlow/Documents/Athletics/Markings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA99DBC-C1B2-C746-A78D-AF74D5CC6C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CE55E3-2C6B-E244-941A-80FC1C4AED97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17380" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="81">
   <si>
     <t>X</t>
   </si>
@@ -305,9 +305,6 @@
   </si>
   <si>
     <t>Lane Widths</t>
-  </si>
-  <si>
-    <t>H-1-6</t>
   </si>
 </sst>
 </file>
@@ -5304,7 +5301,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A868880E-8208-0543-8FC3-12A6987F4D8C}" type="CELLRANGE">
+                    <a:fld id="{47473EC8-0CFA-B74F-8C53-C626E5FFE429}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5336,7 +5333,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{38DDAB1B-3369-2C4F-9F8C-78FF151322D1}" type="CELLRANGE">
+                    <a:fld id="{CE99B4D2-6CF2-F444-8625-342A71F5CC63}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5369,7 +5366,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7A85A29F-2AFA-4244-A8A9-E357182AF61D}" type="CELLRANGE">
+                    <a:fld id="{891362AA-E23B-8C4E-820C-A0427CBE8D7E}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5402,7 +5399,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F5E0A083-2801-CD4D-B9C6-43C24288B82D}" type="CELLRANGE">
+                    <a:fld id="{97EF7E62-8264-264E-9089-B04FD24F7D09}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5435,7 +5432,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EB077C23-02B0-8E47-8F97-DD61B230A7A6}" type="CELLRANGE">
+                    <a:fld id="{8F0E066D-22EF-B045-92FD-9B4944213351}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5468,7 +5465,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{638E16FF-DCF9-9742-B966-85FF90936F68}" type="CELLRANGE">
+                    <a:fld id="{6A9E62C1-EE2C-DC4A-AA2C-6CBD05E8E195}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5501,7 +5498,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6CD9F27B-BBBE-0D4C-9656-057ABEC7B26D}" type="CELLRANGE">
+                    <a:fld id="{41DE611D-8D08-D84A-85A7-2B90BD919BE2}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5534,7 +5531,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3A4C4B3A-183A-6B4F-8139-3A585B848F0F}" type="CELLRANGE">
+                    <a:fld id="{449EF0F9-946E-6D44-B68C-0D5D2140BEAB}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5567,7 +5564,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{070C4772-88FC-994F-B1D4-2AA0B33FA836}" type="CELLRANGE">
+                    <a:fld id="{72DA3D23-22C0-CB43-8EAA-3B55C76B8AD7}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5600,7 +5597,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0ADF6AF9-C806-7F40-81BB-D0253400C085}" type="CELLRANGE">
+                    <a:fld id="{57888B07-585C-CB42-8583-6A40F049FD55}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5633,7 +5630,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FD57E198-42D3-154C-B328-7104403C7943}" type="CELLRANGE">
+                    <a:fld id="{479829C3-56D5-3542-83C9-8476AC21FA97}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5666,7 +5663,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1DCB7032-B1CE-BF40-A225-03FF50ADA1F9}" type="CELLRANGE">
+                    <a:fld id="{722ECB52-AA6E-194C-AEE6-1D2B77DC0B70}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5699,7 +5696,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{564062BF-A926-0C44-AE6B-507BE12B65EF}" type="CELLRANGE">
+                    <a:fld id="{5F3CBDB7-7336-1842-90BC-8895D4A3ADD0}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5732,7 +5729,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{919D03D3-3473-414C-9D76-4FA19F650333}" type="CELLRANGE">
+                    <a:fld id="{E82C9668-06DF-8C4F-BF88-4AFF8DA55407}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5765,7 +5762,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DE08BCEB-F3CD-D741-985A-1CDAD1D18F93}" type="CELLRANGE">
+                    <a:fld id="{5CAB54D5-EB81-BB4F-85C9-871CEC87AF38}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5798,7 +5795,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0F07E109-89F1-354E-BA58-1758502BD30B}" type="CELLRANGE">
+                    <a:fld id="{2A9D2575-9F41-AD46-BAB6-EE2EE19039BA}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5831,7 +5828,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{48AAC21C-5C18-6243-8B93-7B3C3A3B1E7A}" type="CELLRANGE">
+                    <a:fld id="{5A2575B4-C24C-B149-B0BF-D85DB9739945}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5864,7 +5861,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{84830C99-3EC1-014D-93CA-4E1FE57FC60A}" type="CELLRANGE">
+                    <a:fld id="{92128CE2-23DA-8E4C-80C4-FB480618F1FD}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5897,7 +5894,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{990ED1D2-9B75-A44F-A4F9-0AAFDEBCE56B}" type="CELLRANGE">
+                    <a:fld id="{CC24E082-193D-4D40-AE9F-968420976124}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5930,7 +5927,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{86C29A59-F955-CA44-B1DC-2709254D014D}" type="CELLRANGE">
+                    <a:fld id="{6DC3B6C5-BE4F-DB41-8DF4-BE71FEFAB0CB}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5963,7 +5960,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0836884E-DF84-244F-8D04-42E8DF9256E7}" type="CELLRANGE">
+                    <a:fld id="{416A85C5-8EE1-094C-8B55-FF4AAC40B4AB}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9134,7 +9131,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0893B05A-4ACA-454B-BB40-B5260470C859}" type="CELLRANGE">
+                    <a:fld id="{551BDB5B-2BA4-8B42-A849-4BE54E2D47EA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9244,10 +9241,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>76.89</c:v>
+                  <c:v>119.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>120.35708960898624</c:v>
+                  <c:v>-50.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9259,10 +9256,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>38.99</c:v>
+                  <c:v>25.67</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.98833687065725</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9275,7 +9272,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>51.17</c:v>
+                    <c:v>172.24</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -10398,15 +10395,15 @@
         <v>74</v>
       </c>
       <c r="T3" s="40" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="U3" s="42">
         <f>IFERROR(VLOOKUP(T3,AllPoints,2,FALSE),0)</f>
-        <v>76.89</v>
+        <v>119.75</v>
       </c>
       <c r="V3" s="43">
         <f>IFERROR(VLOOKUP(T3,AllPoints,3,FALSE),0)</f>
-        <v>38.99</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="4" spans="19:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -10414,15 +10411,15 @@
         <v>75</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="U4" s="44">
         <f>IFERROR(VLOOKUP(T4,AllPoints,2,FALSE),0)</f>
-        <v>120.35708960898624</v>
+        <v>-50.57</v>
       </c>
       <c r="V4" s="45">
         <f>IFERROR(VLOOKUP(T4,AllPoints,3,FALSE),0)</f>
-        <v>11.98833687065725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="19:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -10431,15 +10428,15 @@
       </c>
       <c r="T5" s="41">
         <f>SQRT((U4-U3)^2+(V4-V3)^2)</f>
-        <v>51.171063022240872</v>
+        <v>172.24358130275857</v>
       </c>
       <c r="U5" s="44">
         <f>ABS(U4-U3)</f>
-        <v>43.467089608986242</v>
+        <v>170.32</v>
       </c>
       <c r="V5" s="45">
         <f>ABS(V4-V3)</f>
-        <v>27.001663129342752</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="15" spans="19:22" x14ac:dyDescent="0.2">

--- a/DunbarLayout.xlsx
+++ b/DunbarLayout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevenbarlow/Documents/Athletics/Markings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CE55E3-2C6B-E244-941A-80FC1C4AED97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B2BB44-1ECC-A147-8FAD-25C75F6F5D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="29400" windowHeight="17340" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="83">
   <si>
     <t>X</t>
   </si>
@@ -305,6 +305,12 @@
   </si>
   <si>
     <t>Lane Widths</t>
+  </si>
+  <si>
+    <t>Pack Start</t>
+  </si>
+  <si>
+    <t>Manually Entered (Based on 3000m offsets)</t>
   </si>
 </sst>
 </file>
@@ -5301,7 +5307,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{47473EC8-0CFA-B74F-8C53-C626E5FFE429}" type="CELLRANGE">
+                    <a:fld id="{D4D21C8C-4550-C84B-91F5-843380875269}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5333,7 +5339,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CE99B4D2-6CF2-F444-8625-342A71F5CC63}" type="CELLRANGE">
+                    <a:fld id="{9A77649F-9129-FE49-8944-196A7CBFE403}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5366,7 +5372,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{891362AA-E23B-8C4E-820C-A0427CBE8D7E}" type="CELLRANGE">
+                    <a:fld id="{3EEE9F26-D67C-D041-9CA1-2E84FFB954EE}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5399,7 +5405,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{97EF7E62-8264-264E-9089-B04FD24F7D09}" type="CELLRANGE">
+                    <a:fld id="{C2031E23-EDF7-2444-A97F-B1F857EC5915}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5432,7 +5438,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8F0E066D-22EF-B045-92FD-9B4944213351}" type="CELLRANGE">
+                    <a:fld id="{A0108B92-E2E9-BE42-A7D3-478D2DDC14A9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5465,7 +5471,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A9E62C1-EE2C-DC4A-AA2C-6CBD05E8E195}" type="CELLRANGE">
+                    <a:fld id="{ED889AD6-3C42-F947-A24C-022F5592E8E1}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5498,7 +5504,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{41DE611D-8D08-D84A-85A7-2B90BD919BE2}" type="CELLRANGE">
+                    <a:fld id="{AB27BB80-F97F-8142-8543-F37A3E50BA37}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5531,7 +5537,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{449EF0F9-946E-6D44-B68C-0D5D2140BEAB}" type="CELLRANGE">
+                    <a:fld id="{647F00C3-9CCA-5146-9CFF-0EBD5CFF5C39}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5564,7 +5570,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{72DA3D23-22C0-CB43-8EAA-3B55C76B8AD7}" type="CELLRANGE">
+                    <a:fld id="{E6FB0027-C2E7-EC40-AB43-1DF904354BAA}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5597,7 +5603,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{57888B07-585C-CB42-8583-6A40F049FD55}" type="CELLRANGE">
+                    <a:fld id="{AEFDB63B-BFDA-5944-B4BA-01D6C5DD2047}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5630,7 +5636,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{479829C3-56D5-3542-83C9-8476AC21FA97}" type="CELLRANGE">
+                    <a:fld id="{9D4025C1-001D-5F40-8FDF-2DED473BA4EB}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5663,7 +5669,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{722ECB52-AA6E-194C-AEE6-1D2B77DC0B70}" type="CELLRANGE">
+                    <a:fld id="{92E44D20-7109-B442-8DDB-F13E1D04A73D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5696,7 +5702,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5F3CBDB7-7336-1842-90BC-8895D4A3ADD0}" type="CELLRANGE">
+                    <a:fld id="{FBC41DCB-DEBB-5C4C-8F57-7EA98EB1BB4D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5729,7 +5735,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E82C9668-06DF-8C4F-BF88-4AFF8DA55407}" type="CELLRANGE">
+                    <a:fld id="{CC35C747-7DF9-AD4A-89E4-145E8249A549}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5762,7 +5768,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5CAB54D5-EB81-BB4F-85C9-871CEC87AF38}" type="CELLRANGE">
+                    <a:fld id="{D6CB8591-E391-F44E-AB73-E3C76B93CA29}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5795,7 +5801,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A9D2575-9F41-AD46-BAB6-EE2EE19039BA}" type="CELLRANGE">
+                    <a:fld id="{7F1F59CE-A7AB-CA4F-A341-5218780D8278}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5828,7 +5834,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5A2575B4-C24C-B149-B0BF-D85DB9739945}" type="CELLRANGE">
+                    <a:fld id="{3B78752F-D2C2-8949-9A5B-56B311CC1B22}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5861,7 +5867,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{92128CE2-23DA-8E4C-80C4-FB480618F1FD}" type="CELLRANGE">
+                    <a:fld id="{FDC6F91B-682D-DB44-9D0B-71C4AEFFF223}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5894,7 +5900,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CC24E082-193D-4D40-AE9F-968420976124}" type="CELLRANGE">
+                    <a:fld id="{53EFBB64-7FF3-9E4C-99E0-10BD9B6A96C7}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5927,7 +5933,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6DC3B6C5-BE4F-DB41-8DF4-BE71FEFAB0CB}" type="CELLRANGE">
+                    <a:fld id="{E901A295-8D56-1E40-B8A4-F43BBDF8DF5B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5960,7 +5966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{416A85C5-8EE1-094C-8B55-FF4AAC40B4AB}" type="CELLRANGE">
+                    <a:fld id="{CF61254D-5E37-214D-8AA2-C4A03B87F55D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9131,7 +9137,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{551BDB5B-2BA4-8B42-A849-4BE54E2D47EA}" type="CELLRANGE">
+                    <a:fld id="{14E94B45-F188-A44D-AD81-C9023905F660}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9241,10 +9247,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>119.75</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-50.57</c:v>
+                  <c:v>76.89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9256,10 +9262,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>25.67</c:v>
+                  <c:v>-38.99</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-38.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9272,13 +9278,132 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>172.24</c:v>
+                    <c:v>76.89</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-2BC8-004C-99B4-3A00BCD522DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="31"/>
+          <c:order val="31"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Starts!$Z$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pack Start</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Starts!$AC$3:$AC$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>76.89</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>77.061759131563562</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>77.414502168943088</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>77.927245206322638</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78.529988243702192</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>79.242731281081731</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80.065474318461256</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>81.028217355840823</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>82.16096039322035</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Starts!$AD$3:$AD$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>-38.99</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-40.21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-41.43</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-42.65</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-43.87</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-45.089999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-46.309999999999995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-47.529999999999994</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-48.749999999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9C3F-8F4D-AC88-4AC71AF42F75}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9436,6 +9561,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9443,7 +9569,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10395,15 +10520,15 @@
         <v>74</v>
       </c>
       <c r="T3" s="40" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="U3" s="42">
         <f>IFERROR(VLOOKUP(T3,AllPoints,2,FALSE),0)</f>
-        <v>119.75</v>
+        <v>0</v>
       </c>
       <c r="V3" s="43">
         <f>IFERROR(VLOOKUP(T3,AllPoints,3,FALSE),0)</f>
-        <v>25.67</v>
+        <v>-38.99</v>
       </c>
     </row>
     <row r="4" spans="19:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -10411,15 +10536,15 @@
         <v>75</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="U4" s="44">
         <f>IFERROR(VLOOKUP(T4,AllPoints,2,FALSE),0)</f>
-        <v>-50.57</v>
+        <v>76.89</v>
       </c>
       <c r="V4" s="45">
         <f>IFERROR(VLOOKUP(T4,AllPoints,3,FALSE),0)</f>
-        <v>0</v>
+        <v>-38.99</v>
       </c>
     </row>
     <row r="5" spans="19:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -10428,15 +10553,15 @@
       </c>
       <c r="T5" s="41">
         <f>SQRT((U4-U3)^2+(V4-V3)^2)</f>
-        <v>172.24358130275857</v>
+        <v>76.89</v>
       </c>
       <c r="U5" s="44">
         <f>ABS(U4-U3)</f>
-        <v>170.32</v>
+        <v>76.89</v>
       </c>
       <c r="V5" s="45">
         <f>ABS(V4-V3)</f>
-        <v>25.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="19:22" x14ac:dyDescent="0.2">
@@ -10465,7 +10590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1154C7F8-E501-6946-B4B9-A33A7FDAB29C}">
-  <dimension ref="A1:D243"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -14324,6 +14449,159 @@
       <c r="D243" s="1">
         <f>Hurdles!G82</f>
         <v>-47.529999999999994</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>81</v>
+      </c>
+      <c r="B245" t="str">
+        <f>Starts!Z3</f>
+        <v>PS-1</v>
+      </c>
+      <c r="C245" s="1">
+        <f>Starts!AC3</f>
+        <v>76.89</v>
+      </c>
+      <c r="D245" s="1">
+        <f>Starts!AD3</f>
+        <v>-38.99</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>81</v>
+      </c>
+      <c r="B246" t="str">
+        <f>Starts!Z4</f>
+        <v>PS-2</v>
+      </c>
+      <c r="C246" s="1">
+        <f>Starts!AC4</f>
+        <v>77.061759131563562</v>
+      </c>
+      <c r="D246" s="1">
+        <f>Starts!AD4</f>
+        <v>-40.21</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>81</v>
+      </c>
+      <c r="B247" t="str">
+        <f>Starts!Z5</f>
+        <v>PS-3</v>
+      </c>
+      <c r="C247" s="1">
+        <f>Starts!AC5</f>
+        <v>77.414502168943088</v>
+      </c>
+      <c r="D247" s="1">
+        <f>Starts!AD5</f>
+        <v>-41.43</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>81</v>
+      </c>
+      <c r="B248" t="str">
+        <f>Starts!Z6</f>
+        <v>PS-4</v>
+      </c>
+      <c r="C248" s="1">
+        <f>Starts!AC6</f>
+        <v>77.927245206322638</v>
+      </c>
+      <c r="D248" s="1">
+        <f>Starts!AD6</f>
+        <v>-42.65</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>81</v>
+      </c>
+      <c r="B249" t="str">
+        <f>Starts!Z7</f>
+        <v>PS-5</v>
+      </c>
+      <c r="C249" s="1">
+        <f>Starts!AC7</f>
+        <v>78.529988243702192</v>
+      </c>
+      <c r="D249" s="1">
+        <f>Starts!AD7</f>
+        <v>-43.87</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>81</v>
+      </c>
+      <c r="B250" t="str">
+        <f>Starts!Z8</f>
+        <v>PS-6</v>
+      </c>
+      <c r="C250" s="1">
+        <f>Starts!AC8</f>
+        <v>79.242731281081731</v>
+      </c>
+      <c r="D250" s="1">
+        <f>Starts!AD8</f>
+        <v>-45.089999999999996</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>81</v>
+      </c>
+      <c r="B251" t="str">
+        <f>Starts!Z9</f>
+        <v>PS-7</v>
+      </c>
+      <c r="C251" s="1">
+        <f>Starts!AC9</f>
+        <v>80.065474318461256</v>
+      </c>
+      <c r="D251" s="1">
+        <f>Starts!AD9</f>
+        <v>-46.309999999999995</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>81</v>
+      </c>
+      <c r="B252" t="str">
+        <f>Starts!Z10</f>
+        <v>PS-8</v>
+      </c>
+      <c r="C252" s="1">
+        <f>Starts!AC10</f>
+        <v>81.028217355840823</v>
+      </c>
+      <c r="D252" s="1">
+        <f>Starts!AD10</f>
+        <v>-47.529999999999994</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>81</v>
+      </c>
+      <c r="B253" t="str">
+        <f>Starts!Z11</f>
+        <v>PS-9</v>
+      </c>
+      <c r="C253" s="1">
+        <f>Starts!AC11</f>
+        <v>82.16096039322035</v>
+      </c>
+      <c r="D253" s="1">
+        <f>Starts!AD11</f>
+        <v>-48.749999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -37254,10 +37532,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8595EA5-6D6C-5D4F-A376-800138B80F66}">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -37296,8 +37574,16 @@
       </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -37367,8 +37653,21 @@
       <c r="Y2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>CONCATENATE("200-",C3)</f>
         <v>200-1</v>
@@ -37464,10 +37763,29 @@
         <f t="shared" ref="Y3:Y11" si="12">-VLOOKUP(W3,Data,2,FALSE)*COS(RADIANS(180*(IF(V3&gt;VLOOKUP(W3,Data,8,FALSE),1,IF(V3&gt;VLOOKUP(W3,Data,4,FALSE),(V3-VLOOKUP(W3,Data,4,FALSE))/VLOOKUP(W3,Data,5,FALSE),0)))+180*(IF(V3&gt;VLOOKUP(W3,Data,10,FALSE),1,IF(V3&gt;VLOOKUP(W3,Data,9,FALSE),(V3-VLOOKUP(W3,Data,9,FALSE))/VLOOKUP(W3,Data,7,FALSE),0)))))</f>
         <v>32.402578781011094</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z3" t="str">
+        <f>CONCATENATE("PS-",AB3)</f>
+        <v>PS-1</v>
+      </c>
+      <c r="AA3" s="1">
+        <f>Starts!Q3-Lookups!H2</f>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ref="AC3:AC11" si="13">(Straight-(IF(AA3&gt;VLOOKUP(AB3,Data,4,FALSE),1,AA3/VLOOKUP(AB3,Data,4,FALSE)))*Straight+(IF(AA3&gt;VLOOKUP(AB3,Data,9,FALSE),1,IF(AA3&gt;VLOOKUP(AB3,Data,8,FALSE),(AA3-VLOOKUP(AB3,Data,8,FALSE))/VLOOKUP(AB3,Data,6,FALSE),0)))*Straight)-VLOOKUP(AB3,Data,2,FALSE)*SIN(RADIANS(180*(IF(AA3&gt;VLOOKUP(AB3,Data,8,FALSE),1,IF(AA3&gt;VLOOKUP(AB3,Data,4,FALSE),(AA3-VLOOKUP(AB3,Data,4,FALSE))/VLOOKUP(AB3,Data,5,FALSE),0)))+180*(IF(AA3&gt;VLOOKUP(AB3,Data,10,FALSE),1,IF(AA3&gt;VLOOKUP(AB3,Data,9,FALSE),(AA3-VLOOKUP(AB3,Data,9,FALSE))/VLOOKUP(AB3,Data,7,FALSE),0)))))</f>
+        <v>76.89</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ref="AD3:AD11" si="14">-VLOOKUP(AB3,Data,2,FALSE)*COS(RADIANS(180*(IF(AA3&gt;VLOOKUP(AB3,Data,8,FALSE),1,IF(AA3&gt;VLOOKUP(AB3,Data,4,FALSE),(AA3-VLOOKUP(AB3,Data,4,FALSE))/VLOOKUP(AB3,Data,5,FALSE),0)))+180*(IF(AA3&gt;VLOOKUP(AB3,Data,10,FALSE),1,IF(AA3&gt;VLOOKUP(AB3,Data,9,FALSE),(AA3-VLOOKUP(AB3,Data,9,FALSE))/VLOOKUP(AB3,Data,7,FALSE),0)))))</f>
+        <v>-38.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <f t="shared" ref="A4:A10" si="13">CONCATENATE("200-",C4)</f>
+        <f t="shared" ref="A4:A10" si="15">CONCATENATE("200-",C4)</f>
         <v>200-2</v>
       </c>
       <c r="B4" s="1">
@@ -37486,7 +37804,7 @@
         <v>40.029274186384576</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4:F10" si="14">CONCATENATE("400-",H4)</f>
+        <f t="shared" ref="F4:F10" si="16">CONCATENATE("400-",H4)</f>
         <v>400-2</v>
       </c>
       <c r="G4" s="1">
@@ -37505,7 +37823,7 @@
         <v>-39.488721307572973</v>
       </c>
       <c r="K4" t="str">
-        <f t="shared" ref="K4:K10" si="15">CONCATENATE("800-S-",M4)</f>
+        <f t="shared" ref="K4:K10" si="17">CONCATENATE("800-S-",M4)</f>
         <v>800-S-2</v>
       </c>
       <c r="L4" s="1">
@@ -37524,7 +37842,7 @@
         <v>-40.029274186384576</v>
       </c>
       <c r="P4" t="str">
-        <f t="shared" ref="P4:P11" si="16">CONCATENATE("3000-",R4)</f>
+        <f t="shared" ref="P4:P11" si="18">CONCATENATE("3000-",R4)</f>
         <v>3000-2</v>
       </c>
       <c r="Q4" s="1">
@@ -37542,7 +37860,7 @@
         <v>40.209636783646609</v>
       </c>
       <c r="U4" t="str">
-        <f t="shared" ref="U4:U11" si="17">CONCATENATE("1500-",W4)</f>
+        <f t="shared" ref="U4:U11" si="19">CONCATENATE("1500-",W4)</f>
         <v>1500-2</v>
       </c>
       <c r="V4" s="1">
@@ -37559,10 +37877,29 @@
         <f t="shared" si="12"/>
         <v>33.513454337883516</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z4" t="str">
+        <f t="shared" ref="Z4:Z11" si="20">CONCATENATE("PS-",AB4)</f>
+        <v>PS-2</v>
+      </c>
+      <c r="AA4" s="1">
+        <f>Starts!Q4-Lookups!H3</f>
+        <v>-0.1717591315635616</v>
+      </c>
+      <c r="AB4">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" si="13"/>
+        <v>77.061759131563562</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" si="14"/>
+        <v>-40.21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>200-3</v>
       </c>
       <c r="B5" s="1">
@@ -37581,7 +37918,7 @@
         <v>40.729635545662539</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>400-3</v>
       </c>
       <c r="G5" s="1">
@@ -37600,7 +37937,7 @@
         <v>-38.652221177045483</v>
       </c>
       <c r="K5" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>800-S-3</v>
       </c>
       <c r="L5" s="1">
@@ -37619,7 +37956,7 @@
         <v>-40.727812217394366</v>
       </c>
       <c r="P5" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3000-3</v>
       </c>
       <c r="Q5" s="1">
@@ -37637,7 +37974,7 @@
         <v>41.426711779384561</v>
       </c>
       <c r="U5" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1500-3</v>
       </c>
       <c r="V5" s="1">
@@ -37654,10 +37991,29 @@
         <f t="shared" si="12"/>
         <v>34.714466419543839</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z5" t="str">
+        <f t="shared" si="20"/>
+        <v>PS-3</v>
+      </c>
+      <c r="AA5" s="1">
+        <f>Starts!Q5-Lookups!H4</f>
+        <v>-0.5245021689430871</v>
+      </c>
+      <c r="AB5">
+        <v>3</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="13"/>
+        <v>77.414502168943088</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" si="14"/>
+        <v>-41.43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>200-4</v>
       </c>
       <c r="B6" s="1">
@@ -37676,7 +38032,7 @@
         <v>41.123693321408084</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>400-4</v>
       </c>
       <c r="G6" s="1">
@@ -37695,7 +38051,7 @@
         <v>-36.654016524887396</v>
       </c>
       <c r="K6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>800-S-4</v>
       </c>
       <c r="L6" s="1">
@@ -37714,7 +38070,7 @@
         <v>-41.118411030354849</v>
       </c>
       <c r="P6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3000-4</v>
       </c>
       <c r="Q6" s="1">
@@ -37732,7 +38088,7 @@
         <v>42.637505207341619</v>
       </c>
       <c r="U6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1500-4</v>
       </c>
       <c r="V6" s="1">
@@ -37749,10 +38105,29 @@
         <f t="shared" si="12"/>
         <v>36.004371095334143</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z6" t="str">
+        <f t="shared" si="20"/>
+        <v>PS-4</v>
+      </c>
+      <c r="AA6" s="1">
+        <f>Starts!Q6-Lookups!H5</f>
+        <v>-1.0372452063226376</v>
+      </c>
+      <c r="AB6">
+        <v>4</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="13"/>
+        <v>77.927245206322638</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" si="14"/>
+        <v>-42.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>200-5</v>
       </c>
       <c r="B7" s="1">
@@ -37771,7 +38146,7 @@
         <v>41.242113035118379</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>400-5</v>
       </c>
       <c r="G7" s="1">
@@ -37790,7 +38165,7 @@
         <v>-33.673281860108567</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>800-S-5</v>
       </c>
       <c r="L7" s="1">
@@ -37809,7 +38184,7 @@
         <v>-41.208071253970353</v>
       </c>
       <c r="P7" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3000-5</v>
       </c>
       <c r="Q7" s="1">
@@ -37827,7 +38202,7 @@
         <v>43.839627335827771</v>
       </c>
       <c r="U7" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1500-5</v>
       </c>
       <c r="V7" s="1">
@@ -37844,10 +38219,29 @@
         <f t="shared" si="12"/>
         <v>37.342109859236707</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" t="str">
+        <f t="shared" si="20"/>
+        <v>PS-5</v>
+      </c>
+      <c r="AA7" s="1">
+        <f>Starts!Q7-Lookups!H6</f>
+        <v>-1.6399882437021915</v>
+      </c>
+      <c r="AB7">
+        <v>5</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" si="13"/>
+        <v>78.529988243702192</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" si="14"/>
+        <v>-43.87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>200-6</v>
       </c>
       <c r="B8" s="1">
@@ -37866,7 +38260,7 @@
         <v>41.113366430523136</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>400-6</v>
       </c>
       <c r="G8" s="1">
@@ -37885,7 +38279,7 @@
         <v>-29.884890186314838</v>
       </c>
       <c r="K8" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>800-S-6</v>
       </c>
       <c r="L8" s="1">
@@ -37904,7 +38298,7 @@
         <v>-41.027075451902661</v>
       </c>
       <c r="P8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3000-6</v>
       </c>
       <c r="Q8" s="1">
@@ -37922,7 +38316,7 @@
         <v>45.029173534163057</v>
       </c>
       <c r="U8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1500-6</v>
       </c>
       <c r="V8" s="1">
@@ -37939,10 +38333,29 @@
         <f t="shared" si="12"/>
         <v>38.709527409661149</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" t="str">
+        <f t="shared" si="20"/>
+        <v>PS-6</v>
+      </c>
+      <c r="AA8" s="1">
+        <f>Starts!Q8-Lookups!H7</f>
+        <v>-2.3527312810817307</v>
+      </c>
+      <c r="AB8">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" si="13"/>
+        <v>79.242731281081731</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" si="14"/>
+        <v>-45.089999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>200-7</v>
       </c>
       <c r="B9" s="1">
@@ -37961,7 +38374,7 @@
         <v>40.763638410988712</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>400-7</v>
       </c>
       <c r="G9" s="1">
@@ -37980,7 +38393,7 @@
         <v>-25.453084279932426</v>
       </c>
       <c r="K9" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>800-S-7</v>
       </c>
       <c r="L9" s="1">
@@ -37999,7 +38412,7 @@
         <v>-40.611475028459019</v>
       </c>
       <c r="P9" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3000-7</v>
       </c>
       <c r="Q9" s="1">
@@ -38017,7 +38430,7 @@
         <v>46.20210517762488</v>
       </c>
       <c r="U9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1500-7</v>
       </c>
       <c r="V9" s="1">
@@ -38034,10 +38447,29 @@
         <f t="shared" si="12"/>
         <v>40.154363150076051</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" t="str">
+        <f t="shared" si="20"/>
+        <v>PS-7</v>
+      </c>
+      <c r="AA9" s="1">
+        <f>Starts!Q9-Lookups!H8</f>
+        <v>-3.1754743184612551</v>
+      </c>
+      <c r="AB9">
+        <v>7</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" si="13"/>
+        <v>80.065474318461256</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" si="14"/>
+        <v>-46.309999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>200-8</v>
       </c>
       <c r="B10" s="1">
@@ -38056,7 +38488,7 @@
         <v>40.216838080138508</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>400-8</v>
       </c>
       <c r="G10" s="1">
@@ -38075,7 +38507,7 @@
         <v>-20.527818858156163</v>
       </c>
       <c r="K10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>800-S-8</v>
       </c>
       <c r="L10" s="1">
@@ -38094,7 +38526,7 @@
         <v>-39.986993520288692</v>
       </c>
       <c r="P10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3000-8</v>
       </c>
       <c r="Q10" s="1">
@@ -38112,7 +38544,7 @@
         <v>47.351470709222561</v>
       </c>
       <c r="U10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1500-8</v>
       </c>
       <c r="V10" s="1">
@@ -38129,8 +38561,27 @@
         <f t="shared" si="12"/>
         <v>41.665207803577559</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" t="str">
+        <f t="shared" si="20"/>
+        <v>PS-8</v>
+      </c>
+      <c r="AA10" s="1">
+        <f>Starts!Q10-Lookups!H9</f>
+        <v>-4.1382173558408226</v>
+      </c>
+      <c r="AB10">
+        <v>8</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" si="13"/>
+        <v>81.028217355840823</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" si="14"/>
+        <v>-47.529999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="K11" t="str">
         <f>CONCATENATE("800-B-",M11)</f>
         <v>800-B-1</v>
@@ -38145,7 +38596,7 @@
         <v>38.99</v>
       </c>
       <c r="P11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3000-9</v>
       </c>
       <c r="Q11" s="1">
@@ -38163,7 +38614,7 @@
         <v>48.467642676186379</v>
       </c>
       <c r="U11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1500-9</v>
       </c>
       <c r="V11" s="1">
@@ -38180,10 +38631,29 @@
         <f t="shared" si="12"/>
         <v>43.253394807187931</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" t="str">
+        <f t="shared" si="20"/>
+        <v>PS-9</v>
+      </c>
+      <c r="AA11" s="1">
+        <f>Starts!Q11-Lookups!H10</f>
+        <v>-5.2709603932203493</v>
+      </c>
+      <c r="AB11">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" si="13"/>
+        <v>82.16096039322035</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" si="14"/>
+        <v>-48.749999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="K12" t="str">
-        <f t="shared" ref="K12:K19" si="18">CONCATENATE("800-B-",M12)</f>
+        <f t="shared" ref="K12:K19" si="21">CONCATENATE("800-B-",M12)</f>
         <v>800-B-2</v>
       </c>
       <c r="M12">
@@ -38197,9 +38667,9 @@
         <v>40.21</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="K13" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>800-B-3</v>
       </c>
       <c r="M13">
@@ -38210,13 +38680,13 @@
         <v>76.88</v>
       </c>
       <c r="O13">
-        <f t="shared" ref="O13:O19" si="19">O12+1.22</f>
+        <f t="shared" ref="O13:O19" si="22">O12+1.22</f>
         <v>41.43</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="K14" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>800-B-4</v>
       </c>
       <c r="M14">
@@ -38227,13 +38697,13 @@
         <v>76.87</v>
       </c>
       <c r="O14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>42.65</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="K15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>800-B-5</v>
       </c>
       <c r="M15">
@@ -38244,13 +38714,13 @@
         <v>76.790000000000006</v>
       </c>
       <c r="O15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>43.87</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="K16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>800-B-6</v>
       </c>
       <c r="M16">
@@ -38261,13 +38731,13 @@
         <v>76.680000000000007</v>
       </c>
       <c r="O16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>45.089999999999996</v>
       </c>
     </row>
     <row r="17" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K17" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>800-B-7</v>
       </c>
       <c r="M17">
@@ -38278,13 +38748,13 @@
         <v>76.570000000000007</v>
       </c>
       <c r="O17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>46.309999999999995</v>
       </c>
     </row>
     <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>800-B-8</v>
       </c>
       <c r="M18">
@@ -38295,13 +38765,13 @@
         <v>76.459999999999994</v>
       </c>
       <c r="O18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>47.529999999999994</v>
       </c>
     </row>
     <row r="19" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K19" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>800-B-9</v>
       </c>
       <c r="M19">
@@ -38312,7 +38782,7 @@
         <v>76.33</v>
       </c>
       <c r="O19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>48.749999999999993</v>
       </c>
     </row>

--- a/DunbarLayout.xlsx
+++ b/DunbarLayout.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevenbarlow/Documents/Athletics/Markings/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevenbarlow/code/rydeAthletics/markings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B2BB44-1ECC-A147-8FAD-25C75F6F5D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5B0174-E7D0-4F40-A526-6180BFF6D745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="29400" windowHeight="17340" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17340" xr2:uid="{E8AB9068-D317-4044-92F0-9148BCE181C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="84">
   <si>
     <t>X</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Manually Entered (Based on 3000m offsets)</t>
+  </si>
+  <si>
+    <t>H-3-3</t>
   </si>
 </sst>
 </file>
@@ -5307,7 +5310,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D4D21C8C-4550-C84B-91F5-843380875269}" type="CELLRANGE">
+                    <a:fld id="{8DC4BDFF-FB6A-604A-8373-D29B98B5183A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5339,7 +5342,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9A77649F-9129-FE49-8944-196A7CBFE403}" type="CELLRANGE">
+                    <a:fld id="{720E5872-3295-5D45-A69F-D3026C3AD0C9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5372,7 +5375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3EEE9F26-D67C-D041-9CA1-2E84FFB954EE}" type="CELLRANGE">
+                    <a:fld id="{56A95304-188D-3948-96C7-2AA9B0A53C5A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5405,7 +5408,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C2031E23-EDF7-2444-A97F-B1F857EC5915}" type="CELLRANGE">
+                    <a:fld id="{BE3B9D91-61AD-B540-8427-63511E4DA587}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5438,7 +5441,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A0108B92-E2E9-BE42-A7D3-478D2DDC14A9}" type="CELLRANGE">
+                    <a:fld id="{7045F69A-542C-D449-A1CC-0D405EEFFFA9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5471,7 +5474,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ED889AD6-3C42-F947-A24C-022F5592E8E1}" type="CELLRANGE">
+                    <a:fld id="{2EA3ABE9-A12C-0240-A567-D39B1CEE72FF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5504,7 +5507,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AB27BB80-F97F-8142-8543-F37A3E50BA37}" type="CELLRANGE">
+                    <a:fld id="{62ADDF93-CFD5-654B-88D2-7357F31C8BC6}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5537,7 +5540,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{647F00C3-9CCA-5146-9CFF-0EBD5CFF5C39}" type="CELLRANGE">
+                    <a:fld id="{237083D9-665A-B34E-AD92-1FD417022357}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5570,7 +5573,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E6FB0027-C2E7-EC40-AB43-1DF904354BAA}" type="CELLRANGE">
+                    <a:fld id="{434158FF-0A2F-CF4C-BA6D-D91899FC1F72}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5603,7 +5606,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AEFDB63B-BFDA-5944-B4BA-01D6C5DD2047}" type="CELLRANGE">
+                    <a:fld id="{63090BC9-C39A-6D4E-910F-4CFC218573D7}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5636,7 +5639,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D4025C1-001D-5F40-8FDF-2DED473BA4EB}" type="CELLRANGE">
+                    <a:fld id="{5D317C30-D6DD-D540-A319-804CDC166CF4}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5669,7 +5672,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{92E44D20-7109-B442-8DDB-F13E1D04A73D}" type="CELLRANGE">
+                    <a:fld id="{509CE872-7EE3-2F45-9FE9-2DF41AB71739}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5702,7 +5705,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FBC41DCB-DEBB-5C4C-8F57-7EA98EB1BB4D}" type="CELLRANGE">
+                    <a:fld id="{ADECF9B2-05ED-2D47-A9FB-7E4EAA3897FB}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5735,7 +5738,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CC35C747-7DF9-AD4A-89E4-145E8249A549}" type="CELLRANGE">
+                    <a:fld id="{9CE3ECEF-6625-6F4F-B52C-5AE1EA3F69DF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5768,7 +5771,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D6CB8591-E391-F44E-AB73-E3C76B93CA29}" type="CELLRANGE">
+                    <a:fld id="{A56E5C08-4FAB-9941-A9FF-3BC90AA38388}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5801,7 +5804,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7F1F59CE-A7AB-CA4F-A341-5218780D8278}" type="CELLRANGE">
+                    <a:fld id="{46C1D3D6-F148-2A47-9DA7-9C9D91D4B640}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5834,7 +5837,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3B78752F-D2C2-8949-9A5B-56B311CC1B22}" type="CELLRANGE">
+                    <a:fld id="{3048942E-5566-E04D-84EE-22D959210FB4}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5867,7 +5870,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FDC6F91B-682D-DB44-9D0B-71C4AEFFF223}" type="CELLRANGE">
+                    <a:fld id="{ACCF54C0-CA22-F742-9660-B5E1AFFF6B91}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5900,7 +5903,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{53EFBB64-7FF3-9E4C-99E0-10BD9B6A96C7}" type="CELLRANGE">
+                    <a:fld id="{08D9F3E8-70B8-C04D-A0FE-C5E95925E628}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5933,7 +5936,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E901A295-8D56-1E40-B8A4-F43BBDF8DF5B}" type="CELLRANGE">
+                    <a:fld id="{8EC6A544-4A60-EA4E-B485-CF1EFDC07B03}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5966,7 +5969,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CF61254D-5E37-214D-8AA2-C4A03B87F55D}" type="CELLRANGE">
+                    <a:fld id="{3AFBF3E7-E814-2940-9DAA-AB6DE41F97E2}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9137,7 +9140,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{14E94B45-F188-A44D-AD81-C9023905F660}" type="CELLRANGE">
+                    <a:fld id="{8FEDF7F9-8DEA-E34D-BAE0-833C206D1887}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9250,7 +9253,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>76.89</c:v>
+                  <c:v>77.336183184677466</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9265,7 +9268,7 @@
                   <c:v>-38.99</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-38.99</c:v>
+                  <c:v>41.42759733035107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9278,7 +9281,7 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="1"/>
                   <c:pt idx="0">
-                    <c:v>76.89</c:v>
+                    <c:v>111.57</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -10536,15 +10539,15 @@
         <v>75</v>
       </c>
       <c r="T4" s="40" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="U4" s="44">
         <f>IFERROR(VLOOKUP(T4,AllPoints,2,FALSE),0)</f>
-        <v>76.89</v>
+        <v>77.336183184677466</v>
       </c>
       <c r="V4" s="45">
         <f>IFERROR(VLOOKUP(T4,AllPoints,3,FALSE),0)</f>
-        <v>-38.99</v>
+        <v>41.42759733035107</v>
       </c>
     </row>
     <row r="5" spans="19:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -10553,15 +10556,15 @@
       </c>
       <c r="T5" s="41">
         <f>SQRT((U4-U3)^2+(V4-V3)^2)</f>
-        <v>76.89</v>
+        <v>111.57004611436027</v>
       </c>
       <c r="U5" s="44">
         <f>ABS(U4-U3)</f>
-        <v>76.89</v>
+        <v>77.336183184677466</v>
       </c>
       <c r="V5" s="45">
         <f>ABS(V4-V3)</f>
-        <v>0</v>
+        <v>80.417597330351072</v>
       </c>
     </row>
     <row r="15" spans="19:22" x14ac:dyDescent="0.2">
